--- a/outputs/38969.xlsx
+++ b/outputs/38969.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="5">
   <si>
     <t xml:space="preserve">Remarks</t>
   </si>
@@ -31,19 +31,10 @@
     <t xml:space="preserve">Difference</t>
   </si>
   <si>
-    <t xml:space="preserve">07XXXCT5131X1ZZ | BLR28444</t>
+    <t xml:space="preserve">Upload</t>
   </si>
   <si>
-    <t xml:space="preserve">24XXXCT5131X1Z3 | BLR28445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29XXXCT5131X1ZT | BLR28446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07XXXCT5131X1ZZ | BLR28447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27XXXCT5131X1ZX | BLR28448</t>
+    <t xml:space="preserve">Do not Upload</t>
   </si>
 </sst>
 </file>
@@ -362,237 +353,204 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R2" s="1" t="str">
+      <c r="R2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S2" s="1" t="str">
         <f aca="false">IF(ISERROR(S2),"Upload",IF(AND(U2&gt;=-1,U2&lt;=1),"Do not Upload","to Check"))</f>
         <v>Upload</v>
-      </c>
-      <c r="S2" s="1" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>4746902.84</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R3" s="1" t="str">
+      <c r="R3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S3" s="1" t="str">
         <f aca="false">IF(ISERROR(S3),"Upload",IF(AND(U3&gt;=-1,U3&lt;=1),"Do not Upload","to Check"))</f>
         <v>Upload</v>
-      </c>
-      <c r="S3" s="1" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
       </c>
       <c r="U3" s="3" t="n">
         <v>-22553.12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R4" s="1" t="str">
+      <c r="R4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S4" s="1" t="str">
         <f aca="false">IF(ISERROR(S4),"Upload",IF(AND(U4&gt;=-1,U4&lt;=1),"Do not Upload","to Check"))</f>
         <v>Upload</v>
-      </c>
-      <c r="S4" s="1" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>-39462.66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R5" s="1" t="str">
+      <c r="R5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S5" s="1" t="str">
         <f aca="false">IF(ISERROR(S5),"Upload",IF(AND(U5&gt;=-1,U5&lt;=1),"Do not Upload","to Check"))</f>
         <v>Upload</v>
-      </c>
-      <c r="S5" s="1" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>-261908.29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R6" s="1" t="str">
+      <c r="R6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S6" s="1" t="str">
         <f aca="false">IF(ISERROR(S6),"Upload",IF(AND(U6&gt;=-1,U6&lt;=1),"Do not Upload","to Check"))</f>
         <v>Upload</v>
-      </c>
-      <c r="S6" s="1" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>-14794.53</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R7" s="1" t="str">
+      <c r="R7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="1" t="str">
         <f aca="false">IF(ISERROR(S7),"Upload",IF(AND(U7&gt;=-1,U7&lt;=1),"Do not Upload","to Check"))</f>
         <v>Upload</v>
-      </c>
-      <c r="S7" s="1" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>-12593.64</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R8" s="1" t="str">
+      <c r="R8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="1" t="str">
         <f aca="false">IF(ISERROR(S8),"Upload",IF(AND(U8&gt;=-1,U8&lt;=1),"Do not Upload","to Check"))</f>
         <v>Upload</v>
-      </c>
-      <c r="S8" s="1" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>-605590.29</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R9" s="1" t="str">
+      <c r="R9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="1" t="str">
         <f aca="false">IF(ISERROR(S9),"Upload",IF(AND(U9&gt;=-1,U9&lt;=1),"Do not Upload","to Check"))</f>
         <v>Upload</v>
-      </c>
-      <c r="S9" s="1" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>-96197.98</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R10" s="1" t="str">
+      <c r="R10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="1" t="str">
         <f aca="false">IF(ISERROR(S10),"Upload",IF(AND(U10&gt;=-1,U10&lt;=1),"Do not Upload","to Check"))</f>
         <v>Upload</v>
-      </c>
-      <c r="S10" s="1" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>-130013.51</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R11" s="1" t="str">
+      <c r="R11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S11" s="1" t="str">
         <f aca="false">IF(ISERROR(S11),"Upload",IF(AND(U11&gt;=-1,U11&lt;=1),"Do not Upload","to Check"))</f>
-        <v>Do not Upload</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>3</v>
+        <v>Upload</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R12" s="1" t="str">
+      <c r="R12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="1" t="str">
         <f aca="false">IF(ISERROR(S12),"Upload",IF(AND(U12&gt;=-1,U12&lt;=1),"Do not Upload","to Check"))</f>
-        <v>Do not Upload</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>3</v>
+        <v>Upload</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R13" s="1" t="str">
+      <c r="S13" s="1" t="str">
         <f aca="false">IF(ISERROR(S13),"Upload",IF(AND(U13&gt;=-1,U13&lt;=1),"Do not Upload","to Check"))</f>
-        <v>Do not Upload</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>4</v>
+        <v>Upload</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R14" s="1" t="str">
+      <c r="S14" s="1" t="str">
         <f aca="false">IF(ISERROR(S14),"Upload",IF(AND(U14&gt;=-1,U14&lt;=1),"Do not Upload","to Check"))</f>
-        <v>Do not Upload</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>4</v>
+        <v>Upload</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R15" s="1" t="str">
+      <c r="S15" s="1" t="str">
         <f aca="false">IF(ISERROR(S15),"Upload",IF(AND(U15&gt;=-1,U15&lt;=1),"Do not Upload","to Check"))</f>
-        <v>to Check</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>5</v>
+        <v>Upload</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R16" s="1" t="str">
+      <c r="S16" s="1" t="str">
         <f aca="false">IF(ISERROR(S16),"Upload",IF(AND(U16&gt;=-1,U16&lt;=1),"Do not Upload","to Check"))</f>
-        <v>Do not Upload</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>5</v>
+        <v>Upload</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R17" s="1" t="str">
+      <c r="S17" s="1" t="str">
         <f aca="false">IF(ISERROR(S17),"Upload",IF(AND(U17&gt;=-1,U17&lt;=1),"Do not Upload","to Check"))</f>
-        <v>Do not Upload</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>6</v>
+        <v>Upload</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R18" s="1" t="str">
+      <c r="S18" s="1" t="str">
         <f aca="false">IF(ISERROR(S18),"Upload",IF(AND(U18&gt;=-1,U18&lt;=1),"Do not Upload","to Check"))</f>
-        <v>Do not Upload</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>6</v>
+        <v>Upload</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R19" s="1" t="str">
+      <c r="S19" s="1" t="str">
         <f aca="false">IF(ISERROR(S19),"Upload",IF(AND(U19&gt;=-1,U19&lt;=1),"Do not Upload","to Check"))</f>
-        <v>to Check</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>7</v>
+        <v>Upload</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="R20" s="1" t="str">
+      <c r="S20" s="1" t="str">
         <f aca="false">IF(ISERROR(S20),"Upload",IF(AND(U20&gt;=-1,U20&lt;=1),"Do not Upload","to Check"))</f>
-        <v>Do not Upload</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>7</v>
+        <v>Upload</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>0</v>
